--- a/docs/forge-and-fable-card-set.xlsx
+++ b/docs/forge-and-fable-card-set.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="443">
   <si>
     <t>ID</t>
   </si>
@@ -392,6 +392,135 @@
     <t>The pact always extracts a throne.</t>
   </si>
   <si>
+    <t>copper_scout</t>
+  </si>
+  <si>
+    <t>Copper Scout</t>
+  </si>
+  <si>
+    <t>Clockwork Compact</t>
+  </si>
+  <si>
+    <t>Swift, Charge</t>
+  </si>
+  <si>
+    <t>Swift. Charge 1 — attacks once then retired. On Death: Draw 1.</t>
+  </si>
+  <si>
+    <t>One precise strike. No regrets.</t>
+  </si>
+  <si>
+    <t>wind_up_soldier</t>
+  </si>
+  <si>
+    <t>Wind-Up Soldier</t>
+  </si>
+  <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Charge 2 — can attack twice before winding down.</t>
+  </si>
+  <si>
+    <t>Wound tight. Released.</t>
+  </si>
+  <si>
+    <t>tinker_drone</t>
+  </si>
+  <si>
+    <t>Tinker Drone</t>
+  </si>
+  <si>
+    <t>On Play: Give a random ally +1 ATK.</t>
+  </si>
+  <si>
+    <t>It improves what it touches.</t>
+  </si>
+  <si>
+    <t>clockwork_siege</t>
+  </si>
+  <si>
+    <t>Clockwork Siege</t>
+  </si>
+  <si>
+    <t>Deal 2 damage to all enemies.</t>
+  </si>
+  <si>
+    <t>Precision bombardment. Always on schedule.</t>
+  </si>
+  <si>
+    <t>pressure_valve</t>
+  </si>
+  <si>
+    <t>Pressure Valve</t>
+  </si>
+  <si>
+    <t>Anchor. On Play: All allies gain +1 HP.</t>
+  </si>
+  <si>
+    <t>Holds the line while others spend themselves.</t>
+  </si>
+  <si>
+    <t>overclock</t>
+  </si>
+  <si>
+    <t>Overclock</t>
+  </si>
+  <si>
+    <t>All allies gain +2 ATK.</t>
+  </si>
+  <si>
+    <t>Push the limits. Worry later.</t>
+  </si>
+  <si>
+    <t>gear_striker</t>
+  </si>
+  <si>
+    <t>Gear Striker</t>
+  </si>
+  <si>
+    <t>Swift. Charge 2 — two fast attacks before gears lock.</t>
+  </si>
+  <si>
+    <t>The mechanism does not tire. Then it stops.</t>
+  </si>
+  <si>
+    <t>gear_forge</t>
+  </si>
+  <si>
+    <t>Gear Forge</t>
+  </si>
+  <si>
+    <t>ENV: Deal 1 damage to a random enemy each turn.</t>
+  </si>
+  <si>
+    <t>The pistons never stop.</t>
+  </si>
+  <si>
+    <t>spring_loaded</t>
+  </si>
+  <si>
+    <t>Spring Loaded</t>
+  </si>
+  <si>
+    <t>Swift. Charge 2 — two 5-ATK attacks. Becomes a blocker when spent.</t>
+  </si>
+  <si>
+    <t>The spring was always going to snap.</t>
+  </si>
+  <si>
+    <t>overclock_titan</t>
+  </si>
+  <si>
+    <t>Overclock Titan</t>
+  </si>
+  <si>
+    <t>Charge 3 — three attacks at 6 ATK. On Play: All allies get +1 ATK.</t>
+  </si>
+  <si>
+    <t>Three strikes. Then it rests. That was always enough.</t>
+  </si>
+  <si>
     <t>spartan_recruit</t>
   </si>
   <si>
@@ -680,9 +809,6 @@
     <t>Iron Vanguard</t>
   </si>
   <si>
-    <t>Anchor. On Play: All allies gain +1 HP.</t>
-  </si>
-  <si>
     <t>The front never breaks while she holds.</t>
   </si>
   <si>
@@ -959,9 +1085,6 @@
     <t>Tanglewood Trap</t>
   </si>
   <si>
-    <t>Deal 2 damage to all enemies.</t>
-  </si>
-  <si>
     <t>The forest does not warn.</t>
   </si>
   <si>
@@ -987,6 +1110,117 @@
   </si>
   <si>
     <t>Before the war, it was a sapling.</t>
+  </si>
+  <si>
+    <t>void_offering</t>
+  </si>
+  <si>
+    <t>Void Offering</t>
+  </si>
+  <si>
+    <t>Veilborn Wastes</t>
+  </si>
+  <si>
+    <t>Discard 1 card. Heal hero for 3. [Triggers Haunt]</t>
+  </si>
+  <si>
+    <t>A gift to the nothing. The nothing repays.</t>
+  </si>
+  <si>
+    <t>grave_whisper</t>
+  </si>
+  <si>
+    <t>Grave Whisper</t>
+  </si>
+  <si>
+    <t>Discard 1 card. Draw 1 card. [Triggers Haunt]</t>
+  </si>
+  <si>
+    <t>The void takes. The void gives.</t>
+  </si>
+  <si>
+    <t>haunt_harbinger</t>
+  </si>
+  <si>
+    <t>Haunt Harbinger</t>
+  </si>
+  <si>
+    <t>Haunt</t>
+  </si>
+  <si>
+    <t>Haunt — each card you discard while this is on board spawns a 1/1 Specter with Swift.</t>
+  </si>
+  <si>
+    <t>It remembers every loss.</t>
+  </si>
+  <si>
+    <t>veil_walker</t>
+  </si>
+  <si>
+    <t>Veil Walker</t>
+  </si>
+  <si>
+    <t>On Play: Discard 1 card. Gain +1/+1. [Triggers Haunt]</t>
+  </si>
+  <si>
+    <t>It enters lighter than it left.</t>
+  </si>
+  <si>
+    <t>desolate_seer</t>
+  </si>
+  <si>
+    <t>Desolate Seer</t>
+  </si>
+  <si>
+    <t>On Play: Discard up to 2 cards. Draw that many. [Triggers Haunt per discard]</t>
+  </si>
+  <si>
+    <t>She has read the ending. She is at peace with it.</t>
+  </si>
+  <si>
+    <t>specter_horde</t>
+  </si>
+  <si>
+    <t>Specter Horde</t>
+  </si>
+  <si>
+    <t>Spawn 3 Specters with Swift.</t>
+  </si>
+  <si>
+    <t>One whisper becomes a chorus.</t>
+  </si>
+  <si>
+    <t>shade_warden</t>
+  </si>
+  <si>
+    <t>Shade Warden</t>
+  </si>
+  <si>
+    <t>The warden keeps nothing. The warden loses nothing.</t>
+  </si>
+  <si>
+    <t>void_shriek</t>
+  </si>
+  <si>
+    <t>Void Shriek</t>
+  </si>
+  <si>
+    <t>Discard up to 3 cards. Deal 2 damage to enemy hero per card discarded. [Triggers Haunt]</t>
+  </si>
+  <si>
+    <t>The void does not speak. It screams.</t>
+  </si>
+  <si>
+    <t>veil_sovereign</t>
+  </si>
+  <si>
+    <t>Veil Sovereign</t>
+  </si>
+  <si>
+    <t>Haunt. On Play: Discard 1 card, draw 1 card, spawn 2 Specters.</t>
+  </si>
+  <si>
+    <t>She ruled the silence between worlds.</t>
   </si>
   <si>
     <t>Fills gap</t>
@@ -1614,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2574,530 +2808,530 @@
       </c>
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="4">
         <v>1</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="4">
+        <v>2</v>
+      </c>
+      <c r="I27" s="4">
         <v>1</v>
       </c>
-      <c r="I27" s="2">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K27" s="2" t="s">
+      <c r="J27" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M27" s="2" t="s">
+      <c r="K27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M27" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="A28" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="4">
+        <v>2</v>
+      </c>
+      <c r="H28" s="4">
+        <v>3</v>
+      </c>
+      <c r="I28" s="4">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2</v>
+      </c>
+      <c r="H29" s="4">
+        <v>2</v>
+      </c>
+      <c r="I29" s="4">
+        <v>3</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="4">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2</v>
+      </c>
+      <c r="H31" s="4">
         <v>1</v>
       </c>
-      <c r="H28" s="2">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="I31" s="4">
+        <v>4</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" s="4">
+        <v>3</v>
+      </c>
+      <c r="H33" s="4">
+        <v>4</v>
+      </c>
+      <c r="I33" s="4">
+        <v>3</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="4">
+        <v>4</v>
+      </c>
+      <c r="H35" s="4">
+        <v>5</v>
+      </c>
+      <c r="I35" s="4">
+        <v>3</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="4">
+        <v>5</v>
+      </c>
+      <c r="H36" s="4">
+        <v>6</v>
+      </c>
+      <c r="I36" s="4">
+        <v>6</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2</v>
-      </c>
-      <c r="H30" s="2">
-        <v>2</v>
-      </c>
-      <c r="I30" s="2">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="2">
-        <v>3</v>
-      </c>
-      <c r="H31" s="2">
-        <v>2</v>
-      </c>
-      <c r="I31" s="2">
-        <v>5</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="2">
-        <v>3</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="2">
-        <v>2</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="2">
-        <v>2</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="2">
-        <v>4</v>
-      </c>
-      <c r="H35" s="2">
-        <v>5</v>
-      </c>
-      <c r="I35" s="2">
-        <v>3</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="2">
-        <v>4</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G37" s="2">
-        <v>5</v>
-      </c>
-      <c r="H37" s="2">
-        <v>4</v>
-      </c>
-      <c r="I37" s="2">
-        <v>6</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M37" s="2" t="s">
+      <c r="K36" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M36" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="G38" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="M38" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G40" s="2">
-        <v>2</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2</v>
-      </c>
-      <c r="I40" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>15</v>
@@ -3108,37 +3342,37 @@
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G41" s="2">
         <v>2</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>34</v>
+      <c r="H41" s="2">
+        <v>2</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>15</v>
@@ -3149,16 +3383,16 @@
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>17</v>
@@ -3170,16 +3404,16 @@
         <v>3</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>15</v>
@@ -3190,16 +3424,16 @@
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>33</v>
@@ -3220,7 +3454,7 @@
         <v>15</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>15</v>
@@ -3231,37 +3465,37 @@
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="G44" s="2">
-        <v>4</v>
-      </c>
-      <c r="H44" s="2">
-        <v>1</v>
-      </c>
-      <c r="I44" s="2">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>15</v>
@@ -3272,37 +3506,37 @@
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>45</v>
       </c>
       <c r="G45" s="2">
-        <v>5</v>
-      </c>
-      <c r="H45" s="2">
-        <v>2</v>
-      </c>
-      <c r="I45" s="2">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>15</v>
@@ -3313,37 +3547,37 @@
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>88</v>
+      <c r="F46" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="G46" s="2">
+        <v>4</v>
+      </c>
+      <c r="H46" s="2">
         <v>5</v>
       </c>
-      <c r="H46" s="2">
-        <v>2</v>
-      </c>
       <c r="I46" s="2">
         <v>3</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>15</v>
@@ -3354,37 +3588,37 @@
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="G47" s="2">
         <v>4</v>
       </c>
-      <c r="H47" s="2">
-        <v>3</v>
-      </c>
-      <c r="I47" s="2">
-        <v>5</v>
+      <c r="H47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>15</v>
@@ -3395,16 +3629,16 @@
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>54</v>
@@ -3422,10 +3656,10 @@
         <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>15</v>
@@ -3434,62 +3668,62 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="2">
-        <v>2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>2</v>
-      </c>
-      <c r="I50" s="2">
-        <v>3</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M50" s="2" t="s">
+    <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="2">
+        <v>5</v>
+      </c>
+      <c r="H49" s="2">
+        <v>3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>6</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>18</v>
@@ -3497,20 +3731,20 @@
       <c r="G51" s="2">
         <v>2</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>34</v>
+      <c r="H51" s="2">
+        <v>2</v>
+      </c>
+      <c r="I51" s="2">
+        <v>2</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>15</v>
@@ -3518,394 +3752,394 @@
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="2">
+        <v>2</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="2">
-        <v>3</v>
-      </c>
-      <c r="H52" s="2">
-        <v>2</v>
-      </c>
-      <c r="I52" s="2">
+      <c r="G53" s="2">
+        <v>3</v>
+      </c>
+      <c r="H53" s="2">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2">
         <v>4</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L52" s="2" t="s">
+      <c r="J53" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="E54" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F54" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G53" s="4">
-        <v>3</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54" s="4">
-        <v>3</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="M54" s="4" t="s">
+      <c r="G54" s="2">
+        <v>3</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="A55" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G55" s="2">
         <v>4</v>
       </c>
-      <c r="H55" s="4">
-        <v>3</v>
-      </c>
-      <c r="I55" s="4">
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2">
         <v>5</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="M55" s="4" t="s">
+      <c r="J55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M55" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="G56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H56" s="2">
+        <v>2</v>
+      </c>
+      <c r="I56" s="2">
+        <v>4</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G57" s="2">
         <v>5</v>
       </c>
-      <c r="I56" s="2">
-        <v>8</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="M56" s="2" t="s">
+      <c r="H57" s="2">
+        <v>2</v>
+      </c>
+      <c r="I57" s="2">
+        <v>3</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G58" s="2">
+        <v>4</v>
+      </c>
+      <c r="H58" s="2">
+        <v>3</v>
+      </c>
+      <c r="I58" s="2">
+        <v>5</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" s="2">
+        <v>5</v>
+      </c>
+      <c r="H59" s="2">
+        <v>4</v>
+      </c>
+      <c r="I59" s="2">
+        <v>6</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G58" s="2">
-        <v>1</v>
-      </c>
-      <c r="H58" s="2">
-        <v>2</v>
-      </c>
-      <c r="I58" s="2">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="4">
-        <v>2</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G60" s="2">
-        <v>2</v>
-      </c>
-      <c r="H60" s="2">
-        <v>2</v>
-      </c>
-      <c r="I60" s="2">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G61" s="4">
-        <v>3</v>
-      </c>
-      <c r="H61" s="4">
-        <v>2</v>
-      </c>
-      <c r="I61" s="4">
-        <v>3</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="L61" s="4" t="s">
+      <c r="G61" s="2">
+        <v>2</v>
+      </c>
+      <c r="H61" s="2">
+        <v>2</v>
+      </c>
+      <c r="I61" s="2">
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="M61" s="4" t="s">
+      <c r="L61" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="M61" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="G62" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>34</v>
@@ -3917,10 +4151,10 @@
         <v>15</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>15</v>
@@ -3928,25 +4162,25 @@
     </row>
     <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F63" s="8" t="s">
-        <v>45</v>
+      <c r="F63" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2">
         <v>2</v>
@@ -3955,13 +4189,13 @@
         <v>4</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>241</v>
+        <v>89</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>15</v>
@@ -3969,198 +4203,198 @@
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G64" s="4">
+        <v>3</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G65" s="4">
+        <v>3</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G66" s="4">
         <v>4</v>
       </c>
-      <c r="H64" s="4">
-        <v>3</v>
-      </c>
-      <c r="I64" s="4">
-        <v>4</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="M64" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="H66" s="4">
+        <v>3</v>
+      </c>
+      <c r="I66" s="4">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F67" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G67" s="2">
+        <v>6</v>
+      </c>
+      <c r="H67" s="2">
         <v>5</v>
       </c>
-      <c r="H65" s="2">
-        <v>6</v>
-      </c>
-      <c r="I65" s="2">
-        <v>6</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="4">
-        <v>1</v>
-      </c>
-      <c r="H67" s="4">
-        <v>2</v>
-      </c>
-      <c r="I67" s="4">
-        <v>1</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+      <c r="I67" s="2">
+        <v>8</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K67" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="L67" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="2">
-        <v>2</v>
-      </c>
-      <c r="H68" s="2">
-        <v>3</v>
-      </c>
-      <c r="I68" s="2">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="M68" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="H69" s="2">
+        <v>2</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>271</v>
@@ -4173,43 +4407,43 @@
       </c>
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" s="2">
-        <v>3</v>
-      </c>
-      <c r="H70" s="2">
-        <v>2</v>
-      </c>
-      <c r="I70" s="2">
-        <v>3</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K70" s="2" t="s">
+      <c r="C70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="4">
+        <v>2</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="L70" s="2" t="s">
+      <c r="L70" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="M70" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4224,25 +4458,25 @@
         <v>15</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>45</v>
+        <v>17</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G71" s="2">
-        <v>3</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="H71" s="2">
+        <v>2</v>
+      </c>
+      <c r="I71" s="2">
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>279</v>
@@ -4265,19 +4499,19 @@
         <v>28</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F72" s="11" t="s">
-        <v>45</v>
+      <c r="F72" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G72" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I72" s="4">
         <v>3</v>
@@ -4296,82 +4530,123 @@
       </c>
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" s="4">
-        <v>5</v>
-      </c>
-      <c r="H73" s="4">
+      <c r="C73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G73" s="2">
+        <v>3</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G74" s="2">
         <v>4</v>
       </c>
-      <c r="I73" s="4">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="M73" s="4" t="s">
+      <c r="H74" s="2">
+        <v>2</v>
+      </c>
+      <c r="I74" s="2">
+        <v>4</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F75" s="6" t="s">
-        <v>18</v>
+      <c r="F75" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="G75" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I75" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M75" s="4" t="s">
         <v>15</v>
@@ -4379,160 +4654,119 @@
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G76" s="2">
+        <v>5</v>
+      </c>
+      <c r="H76" s="2">
+        <v>6</v>
+      </c>
+      <c r="I76" s="2">
+        <v>6</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G76" s="2">
-        <v>2</v>
-      </c>
-      <c r="H76" s="2">
-        <v>3</v>
-      </c>
-      <c r="I76" s="2">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="s">
+      <c r="G78" s="4">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4">
+        <v>2</v>
+      </c>
+      <c r="I78" s="4">
+        <v>1</v>
+      </c>
+      <c r="J78" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G77" s="2">
-        <v>3</v>
-      </c>
-      <c r="H77" s="2">
-        <v>1</v>
-      </c>
-      <c r="I77" s="2">
-        <v>5</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="2">
-        <v>2</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="L78" s="2" t="s">
+      <c r="K78" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="L78" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M78" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>39</v>
+      <c r="F79" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="G79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>310</v>
@@ -4552,13 +4786,13 @@
         <v>15</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G80" s="2">
         <v>2</v>
@@ -4583,84 +4817,863 @@
       </c>
     </row>
     <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" s="2">
+        <v>3</v>
+      </c>
+      <c r="H81" s="2">
+        <v>2</v>
+      </c>
+      <c r="I81" s="2">
+        <v>3</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G82" s="2">
+        <v>3</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="11" t="s">
+      <c r="D83" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G83" s="4">
         <v>4</v>
       </c>
-      <c r="H81" s="4">
-        <v>3</v>
-      </c>
-      <c r="I81" s="4">
+      <c r="H83" s="4">
+        <v>4</v>
+      </c>
+      <c r="I83" s="4">
+        <v>3</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G84" s="4">
         <v>5</v>
       </c>
-      <c r="J81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="L81" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="M81" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="H84" s="4">
+        <v>4</v>
+      </c>
+      <c r="I84" s="4">
+        <v>5</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E82" s="4" t="s">
+      <c r="D86" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="4">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4">
+        <v>1</v>
+      </c>
+      <c r="I86" s="4">
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="2">
+        <v>2</v>
+      </c>
+      <c r="H87" s="2">
+        <v>3</v>
+      </c>
+      <c r="I87" s="2">
+        <v>2</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="2">
+        <v>3</v>
+      </c>
+      <c r="H88" s="2">
+        <v>1</v>
+      </c>
+      <c r="I88" s="2">
+        <v>5</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G89" s="2">
+        <v>2</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G90" s="2">
+        <v>3</v>
+      </c>
+      <c r="H90" s="2">
+        <v>2</v>
+      </c>
+      <c r="I90" s="2">
+        <v>3</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G91" s="2">
+        <v>2</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G92" s="4">
+        <v>4</v>
+      </c>
+      <c r="H92" s="4">
+        <v>3</v>
+      </c>
+      <c r="I92" s="4">
+        <v>5</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F93" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G93" s="4">
         <v>5</v>
       </c>
-      <c r="H82" s="4">
+      <c r="H93" s="4">
         <v>4</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I93" s="4">
         <v>6</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="L82" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="M82" s="4" t="s">
+      <c r="J93" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="4">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="4">
+        <v>2</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="4">
+        <v>2</v>
+      </c>
+      <c r="H97" s="4">
+        <v>1</v>
+      </c>
+      <c r="I97" s="4">
+        <v>3</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G98" s="4">
+        <v>2</v>
+      </c>
+      <c r="H98" s="4">
+        <v>2</v>
+      </c>
+      <c r="I98" s="4">
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G99" s="4">
+        <v>3</v>
+      </c>
+      <c r="H99" s="4">
+        <v>1</v>
+      </c>
+      <c r="I99" s="4">
+        <v>5</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G100" s="4">
+        <v>3</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G101" s="4">
+        <v>3</v>
+      </c>
+      <c r="H101" s="4">
+        <v>2</v>
+      </c>
+      <c r="I101" s="4">
+        <v>4</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G102" s="4">
+        <v>4</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G103" s="4">
+        <v>5</v>
+      </c>
+      <c r="H103" s="4">
+        <v>4</v>
+      </c>
+      <c r="I103" s="4">
+        <v>6</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="M103" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4673,7 +5686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4715,7 +5728,7 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>323</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4747,7 +5760,7 @@
         <v>29</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>324</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4779,7 +5792,7 @@
         <v>35</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>325</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4811,7 +5824,7 @@
         <v>57</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>326</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4843,7 +5856,7 @@
         <v>75</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>327</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4875,7 +5888,7 @@
         <v>79</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4907,7 +5920,7 @@
         <v>95</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>329</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4939,7 +5952,7 @@
         <v>113</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>330</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -4971,117 +5984,149 @@
         <v>122</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="E13" s="14">
-        <v>3</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="F13" s="14">
+        <v>2</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>332</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>45</v>
+        <v>17</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="E14" s="14">
-        <v>3</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="F14" s="14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="14">
+        <v>2</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>333</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>45</v>
+      <c r="D15" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="E15" s="14">
+        <v>2</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>5</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>89</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>334</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="14">
+        <v>2</v>
+      </c>
+      <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>18</v>
+      <c r="D17" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="E17" s="14">
         <v>2</v>
@@ -5096,18 +6141,18 @@
         <v>15</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>233</v>
+        <v>149</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>335</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>240</v>
+        <v>152</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>17</v>
@@ -5119,187 +6164,219 @@
         <v>3</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>241</v>
+        <v>127</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>336</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="14">
-        <v>4</v>
-      </c>
-      <c r="F19" s="14">
-        <v>3</v>
-      </c>
-      <c r="G19" s="14">
-        <v>4</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>337</v>
+      <c r="E20" s="14">
+        <v>3</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>263</v>
+        <v>126</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>18</v>
+      <c r="D21" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="E21" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G21" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>338</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>263</v>
+        <v>126</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>282</v>
+        <v>164</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="E22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="14">
-        <v>5</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>5</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>340</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="14">
+        <v>3</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>1</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1</v>
-      </c>
-      <c r="G25" s="14">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>341</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>316</v>
+        <v>262</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>17</v>
@@ -5317,45 +6394,589 @@
         <v>5</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>317</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="C27" s="14" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="14">
+        <v>2</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="14">
+        <v>3</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="14">
+        <v>4</v>
+      </c>
+      <c r="F30" s="14">
+        <v>3</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="14">
+        <v>1</v>
+      </c>
+      <c r="F32" s="14">
+        <v>2</v>
+      </c>
+      <c r="G32" s="14">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="14">
+        <v>4</v>
+      </c>
+      <c r="F33" s="14">
+        <v>4</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E34" s="14">
         <v>5</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F34" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="14">
+        <v>1</v>
+      </c>
+      <c r="F36" s="14">
+        <v>1</v>
+      </c>
+      <c r="G36" s="14">
+        <v>2</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="14">
+        <v>4</v>
+      </c>
+      <c r="F37" s="14">
+        <v>3</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="14">
+        <v>5</v>
+      </c>
+      <c r="F38" s="14">
+        <v>4</v>
+      </c>
+      <c r="G38" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>343</v>
+      <c r="H38" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="14">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="14">
+        <v>2</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" s="14">
+        <v>2</v>
+      </c>
+      <c r="F42" s="14">
+        <v>2</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="14">
+        <v>2</v>
+      </c>
+      <c r="F43" s="14">
+        <v>1</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="14">
+        <v>3</v>
+      </c>
+      <c r="F44" s="14">
+        <v>1</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="14">
+        <v>3</v>
+      </c>
+      <c r="F45" s="14">
+        <v>2</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="14">
+        <v>3</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="14">
+        <v>4</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="14">
+        <v>5</v>
+      </c>
+      <c r="F48" s="14">
+        <v>4</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5376,13 +6997,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>422</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>423</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -5390,10 +7011,10 @@
         <v>56</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>347</v>
+        <v>425</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -5401,10 +7022,10 @@
         <v>66</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>349</v>
+        <v>427</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -5412,10 +7033,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>350</v>
+        <v>428</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -5423,32 +7044,32 @@
         <v>19</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>351</v>
+        <v>429</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>352</v>
+        <v>430</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>353</v>
+        <v>431</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -5456,21 +7077,21 @@
         <v>83</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>356</v>
+        <v>434</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5496,7 +7117,7 @@
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>357</v>
+        <v>435</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -5508,7 +7129,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -5529,7 +7150,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -5543,10 +7164,10 @@
     </row>
     <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -5573,15 +7194,15 @@
         <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -5608,15 +7229,15 @@
         <v>56</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>33</v>
@@ -5643,15 +7264,15 @@
         <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>313</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>44</v>
@@ -5678,15 +7299,15 @@
         <v>15</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -5713,15 +7334,15 @@
         <v>15</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -5748,15 +7369,15 @@
         <v>15</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>309</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -5783,15 +7404,15 @@
         <v>15</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>54</v>
@@ -5818,15 +7439,15 @@
         <v>15</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -5853,15 +7474,15 @@
         <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -5888,15 +7509,15 @@
         <v>56</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>264</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
@@ -5923,15 +7544,15 @@
         <v>15</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>33</v>
@@ -5958,15 +7579,15 @@
         <v>15</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>279</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>44</v>
@@ -5993,15 +7614,15 @@
         <v>15</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>54</v>
@@ -6028,15 +7649,15 @@
         <v>56</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -6060,10 +7681,10 @@
         <v>28</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>284</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6086,7 +7707,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="H18" s="24">
         <v>40</v>
@@ -6118,7 +7739,7 @@
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>361</v>
+        <v>439</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -6130,7 +7751,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -6151,7 +7772,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -6585,10 +8206,10 @@
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -6615,15 +8236,15 @@
         <v>15</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>33</v>
@@ -6650,7 +8271,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6673,7 +8294,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="H17" s="25">
         <v>39</v>
@@ -6705,7 +8326,7 @@
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>362</v>
+        <v>440</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -6717,7 +8338,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -6738,7 +8359,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -6752,10 +8373,10 @@
     </row>
     <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -6782,15 +8403,15 @@
         <v>56</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -6814,18 +8435,18 @@
         <v>15</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>33</v>
@@ -6852,15 +8473,15 @@
         <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>44</v>
@@ -6887,15 +8508,15 @@
         <v>15</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -6919,18 +8540,18 @@
         <v>28</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -6954,18 +8575,18 @@
         <v>15</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -6989,18 +8610,18 @@
         <v>28</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>54</v>
@@ -7024,10 +8645,10 @@
         <v>15</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7260,7 +8881,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="H17" s="25">
         <v>38</v>
@@ -7292,7 +8913,7 @@
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>363</v>
+        <v>441</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -7304,7 +8925,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -7325,7 +8946,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -7339,10 +8960,10 @@
     </row>
     <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -7369,15 +8990,15 @@
         <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>33</v>
@@ -7404,15 +9025,15 @@
         <v>15</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
@@ -7439,15 +9060,15 @@
         <v>89</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
@@ -7474,15 +9095,15 @@
         <v>89</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -7509,15 +9130,15 @@
         <v>15</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>44</v>
@@ -7544,15 +9165,15 @@
         <v>15</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>54</v>
@@ -7576,18 +9197,18 @@
         <v>15</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
@@ -7614,15 +9235,15 @@
         <v>15</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -7649,15 +9270,15 @@
         <v>15</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -7684,15 +9305,15 @@
         <v>15</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>309</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>33</v>
@@ -7719,15 +9340,15 @@
         <v>15</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>313</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>44</v>
@@ -7754,15 +9375,15 @@
         <v>15</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>305</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -7789,15 +9410,15 @@
         <v>15</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>54</v>
@@ -7824,7 +9445,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7847,7 +9468,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="H17" s="25">
         <v>38</v>
@@ -7879,7 +9500,7 @@
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>364</v>
+        <v>442</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -7891,7 +9512,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -7912,7 +9533,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -8206,10 +9827,10 @@
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -8236,15 +9857,15 @@
         <v>15</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -8271,15 +9892,15 @@
         <v>15</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
@@ -8306,15 +9927,15 @@
         <v>89</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>33</v>
@@ -8341,15 +9962,15 @@
         <v>15</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -8376,15 +9997,15 @@
         <v>89</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>54</v>
@@ -8408,10 +10029,10 @@
         <v>15</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -8434,7 +10055,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="H17" s="24">
         <v>40</v>
